--- a/output/pdf_financials_xlsx/APPT.xlsx
+++ b/output/pdf_financials_xlsx/APPT.xlsx
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.168335</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.168335</v>
       </c>
     </row>
     <row r="93">
@@ -2666,7 +2666,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>3.168335</v>
       </c>

--- a/output/pdf_financials_xlsx/APPT.xlsx
+++ b/output/pdf_financials_xlsx/APPT.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.387564</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.721281</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.387564</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.467908</v>
+        <v>2.189189</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.452569</v>
+        <v>0.06500499999999999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.287142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/APPT.xlsx
+++ b/output/pdf_financials_xlsx/APPT.xlsx
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.041965</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.07112400000000001</v>
       </c>
     </row>
     <row r="68">
